--- a/samples/sample_02_voltage_scale.xlsx
+++ b/samples/sample_02_voltage_scale.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sample" sheetId="1" r:id="R7a6eaeb325c54762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sample" sheetId="1" r:id="Rf8335527e79749d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -293,7 +293,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="str">
-        <x:v>练习：绘制 time_min 下四组归一化响应，形成论文常见的动力学衰减图。</x:v>
+        <x:v>练习：预设会启用右侧图例、脉冲参考线和 pulse_recovery 的阶梯连接。</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str"/>
       <x:c r="C3" s="5" t="str"/>
@@ -302,7 +302,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="str">
-        <x:v>建议：使用散点连线，比较 control、low_dose、high_dose 和 pulse_recovery。</x:v>
+        <x:v>建议：比较 control、low_dose、high_dose 与 pulse_recovery 的衰减差异。</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str"/>
       <x:c r="C4" s="5" t="str"/>
